--- a/fhir/StructureDefinition-ehealth-videoappointment.xlsx
+++ b/fhir/StructureDefinition-ehealth-videoappointment.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>9.0.1</t>
+    <t>10.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T08:01:32+00:00</t>
+    <t>2026-08-06T13:29:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -361,7 +361,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -809,7 +809,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -909,7 +909,7 @@
     <t>Appointment.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -977,7 +977,7 @@
     <t>example</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/appointment-cancellation-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/appointment-cancellation-reason|4.0.1</t>
   </si>
   <si>
     <t>Appointment.serviceCategory</t>
@@ -989,7 +989,7 @@
     <t>A broad categorization of the service that is to be performed during this appointment.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/service-category</t>
+    <t>http://hl7.org/fhir/ValueSet/service-category|4.0.1</t>
   </si>
   <si>
     <t>n/a, might be inferred from the ServiceDeliveryLocation</t>
@@ -1010,7 +1010,7 @@
     <t>For a provider to provider appointment the code "FOLLOWUP" may be appropriate, as this is expected to be discussing some patient that was seen in the past.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/service-type</t>
+    <t>http://hl7.org/fhir/ValueSet/service-type|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">value:coding.code}
@@ -1253,7 +1253,7 @@
     <t>The specialty of a practitioner that would be required to perform the service requested in this appointment.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/c80-practice-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/c80-practice-codes|4.0.1</t>
   </si>
   <si>
     <t>.performer.AssignedPerson.code</t>
@@ -1307,7 +1307,7 @@
     <t>Appointment.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|Procedure|Observation|ImmunizationRecommendation)
+    <t xml:space="preserve">Reference(Condition|4.0.1|Procedure|4.0.1|Observation|4.0.1|ImmunizationRecommendation|4.0.1)
 </t>
   </si>
   <si>
@@ -1467,7 +1467,7 @@
     <t>Appointment.slot</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Slot)
+    <t xml:space="preserve">Reference(Slot|4.0.1)
 </t>
   </si>
   <si>
@@ -1547,7 +1547,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ServiceRequest)
+    <t xml:space="preserve">Reference(ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -1647,7 +1647,7 @@
     <t>Role of participant in encounter.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-participant-type</t>
+    <t>http://hl7.org/fhir/ValueSet/encounter-participant-type|4.0.1</t>
   </si>
   <si>
     <t>(performer | reusableDevice | subject | location).@typeCode</t>
@@ -2077,7 +2077,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.33984375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="48.55859375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="53.0859375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/fhir/StructureDefinition-ehealth-videoappointment.xlsx
+++ b/fhir/StructureDefinition-ehealth-videoappointment.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.0</t>
+    <t>10.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:29:38+00:00</t>
+    <t>2026-08-11T06:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-videoappointment.xlsx
+++ b/fhir/StructureDefinition-ehealth-videoappointment.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.1</t>
+    <t>10.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T06:44:23+00:00</t>
+    <t>2026-09-10T10:12:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-videoappointment.xlsx
+++ b/fhir/StructureDefinition-ehealth-videoappointment.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.2</t>
+    <t>11.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T10:12:06+00:00</t>
+    <t>2026-10-21T13:41:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-videoappointment.xlsx
+++ b/fhir/StructureDefinition-ehealth-videoappointment.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.0</t>
+    <t>11.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T13:41:32+00:00</t>
+    <t>2026-10-23T09:30:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-videoappointment.xlsx
+++ b/fhir/StructureDefinition-ehealth-videoappointment.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.1</t>
+    <t>11.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T09:30:26+00:00</t>
+    <t>2026-10-29T09:18:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-videoappointment.xlsx
+++ b/fhir/StructureDefinition-ehealth-videoappointment.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.2</t>
+    <t>11.0.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T09:18:06+00:00</t>
+    <t>2026-10-29T11:52:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
